--- a/output/tables/signal_statistics.xlsx
+++ b/output/tables/signal_statistics.xlsx
@@ -510,19 +510,19 @@
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.019</v>
+        <v>0.074</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4709</v>
+        <v>0.5424</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.059</v>
+        <v>0.17</v>
       </c>
       <c r="I3" t="n">
         <v>2.7</v>
@@ -555,7 +555,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5424</v>
+        <v>0.4709</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -600,127 +600,127 @@
         <v>0.5685</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>0.041</v>
+        <v>0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH+BTC</t>
+          <t>BTC+ETH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH+BTC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5569</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.106</v>
+        <v>0.102</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BTC+ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.599</v>
+        <v>0.5569</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>0.022</v>
+        <v>0.167</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>LDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -729,31 +729,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6383</v>
+        <v>0.5947</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LDO</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,31 +762,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5947</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>43</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.023</v>
+        <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.6383</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -840,13 +840,13 @@
         <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.024</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -864,22 +864,22 @@
         <v>0.6129</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05</v>
+        <v>0.143</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -897,22 +897,22 @@
         <v>0.6251</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0.026</v>
+        <v>0.073</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -939,13 +939,13 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -972,13 +972,13 @@
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -996,70 +996,70 @@
         <v>0.535</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0.029</v>
+        <v>0.083</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BTC+ETH+QQQ</t>
+          <t>QQQ+SMH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4542</v>
+        <v>0.4341</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QQQ+SMH</t>
+          <t>BTC+ETH+QQQ</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3692</v>
+        <v>0.4542</v>
       </c>
       <c r="D19" t="n">
         <v>33</v>
@@ -1071,19 +1071,19 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4341</v>
+        <v>0.3692</v>
       </c>
       <c r="D20" t="n">
         <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="21">
@@ -1137,13 +1137,13 @@
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.031</v>
+        <v>0.062</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22">
@@ -1182,67 +1182,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QQQ+SMH</t>
+          <t>BTC+SMH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4395</v>
+        <v>0.4142</v>
       </c>
       <c r="D23" t="n">
         <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0.036</v>
+        <v>0.107</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BTC+SMH</t>
+          <t>QQQ+SMH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4142</v>
+        <v>0.4395</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.074</v>
+        <v>0.036</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="25">
@@ -1269,13 +1269,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0.037</v>
+        <v>0.074</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="26">
